--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486502_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486502_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0381</v>
+        <v>5.8485</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8102</v>
+        <v>1.9905</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2279</v>
+        <v>3.858</v>
       </c>
       <c r="G2" t="n">
         <v>1.0963</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7688</v>
+        <v>0.5792</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2019</v>
+        <v>-0.0216</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9707</v>
+        <v>0.6008</v>
       </c>
       <c r="V2" t="n">
         <v>2.6504</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3249</v>
+        <v>4.7641</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6493</v>
+        <v>1.8728</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6756</v>
+        <v>2.8913</v>
       </c>
       <c r="G3" t="n">
         <v>4.2908</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7262</v>
+        <v>-0.2869</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8784</v>
+        <v>-0.6549</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1522</v>
+        <v>0.368</v>
       </c>
       <c r="V3" t="n">
         <v>0.7602</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1601</v>
+        <v>3.6063</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.3409</v>
+        <v>-1.0489</v>
       </c>
       <c r="F4" t="n">
-        <v>4.501</v>
+        <v>4.6552</v>
       </c>
       <c r="G4" t="n">
         <v>3.6823</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5173</v>
+        <v>-0.0712</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2584</v>
+        <v>0.0337</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.259</v>
+        <v>-0.1049</v>
       </c>
       <c r="V4" t="n">
         <v>4.3454</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0261</v>
+        <v>3.5099</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4822</v>
+        <v>2.8427</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.6672</v>
       </c>
       <c r="G5" t="n">
         <v>4.9424</v>
@@ -844,13 +844,13 @@
         <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9609</v>
+        <v>-0.4771</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.536</v>
+        <v>-0.1754</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4249</v>
+        <v>-0.3016</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9554</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1169</v>
+        <v>1.0843</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0725</v>
+        <v>-0.3745</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0444</v>
+        <v>1.4588</v>
       </c>
       <c r="G6" t="n">
         <v>0.7231</v>
@@ -922,13 +922,13 @@
         <v>0.435</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9795</v>
+        <v>-0.0532</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1406</v>
+        <v>-0.3064</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8389</v>
+        <v>0.2532</v>
       </c>
       <c r="V6" t="n">
         <v>-0.0207</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7938</v>
+        <v>0.8469</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1699</v>
+        <v>-1.6408</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9638</v>
+        <v>2.4877</v>
       </c>
       <c r="G7" t="n">
         <v>0.8068</v>
@@ -1000,13 +1000,13 @@
         <v>1.9576</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4645</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6908</v>
+        <v>0.2199</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2263</v>
+        <v>0.2977</v>
       </c>
       <c r="V7" t="n">
         <v>-1.13</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1268</v>
+        <v>-0.2654</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3525</v>
+        <v>-0.7685</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2257</v>
+        <v>0.5031</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1437</v>
@@ -1078,13 +1078,13 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4181</v>
+        <v>-0.5567</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0154</v>
+        <v>-0.4314</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4027</v>
+        <v>-0.1253</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4683</v>
+        <v>-1.524</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2611</v>
+        <v>-2.3476</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7927</v>
+        <v>0.8236</v>
       </c>
       <c r="G9" t="n">
         <v>0.2356</v>
@@ -1156,13 +1156,13 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1215</v>
+        <v>0.0658</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1971</v>
+        <v>0.1106</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0756</v>
+        <v>-0.0448</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9554</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. CAMACHO DE SÁ</t>
+          <t>A. IZAW BOLAVIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1821</v>
+        <v>-1.6424</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4797</v>
+        <v>-5.03</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2976</v>
+        <v>3.3876</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7661</v>
+        <v>1.6355</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0639</v>
+        <v>1.6331</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.7021</v>
+        <v>0.0024</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.9437</v>
+        <v>-0.4745</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7086</v>
+        <v>-0.6657</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2352</v>
+        <v>0.1912</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1776</v>
+        <v>2.1099</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6446</v>
+        <v>2.2988</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.467</v>
+        <v>-0.1889</v>
       </c>
       <c r="P10" t="n">
-        <v>0.87</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.9151</v>
       </c>
       <c r="R10" t="n">
-        <v>0.87</v>
+        <v>1.9576</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.286</v>
+        <v>0.5492</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.536</v>
+        <v>-0.0961</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2499</v>
+        <v>0.6453</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.8695</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.5443</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. IZAW BOLAVIE</t>
+          <t>N. CAMACHO DE SÁ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2604</v>
+        <v>-1.7783</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.0178</v>
+        <v>-3.0759</v>
       </c>
       <c r="F11" t="n">
-        <v>3.7575</v>
+        <v>1.2976</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6355</v>
+        <v>-2.7661</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6331</v>
+        <v>-0.0639</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0024</v>
+        <v>-2.7021</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4745</v>
+        <v>-2.9437</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6657</v>
+        <v>-0.7086</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1912</v>
+        <v>-2.2352</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1099</v>
+        <v>0.1776</v>
       </c>
       <c r="N11" t="n">
-        <v>2.2988</v>
+        <v>0.6446</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1889</v>
+        <v>-0.467</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.9576</v>
+        <v>0.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9151</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9576</v>
+        <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0688</v>
+        <v>0.1178</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0839</v>
+        <v>-0.1322</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0152</v>
+        <v>0.2499</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8695</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.5443</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4223</v>
+        <v>14.4499</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.607699999999999</v>
+        <v>-7.5802</v>
       </c>
       <c r="F12" t="n">
         <v>22.0301</v>
@@ -1363,13 +1363,13 @@
         <v>-2.5577</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.00250000000000089</v>
+        <v>-0.002500000000000835</v>
       </c>
       <c r="K12" t="n">
         <v>1.9336</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.936299999999999</v>
+        <v>-1.9363</v>
       </c>
       <c r="M12" t="n">
         <v>14.5057</v>
@@ -1390,13 +1390,13 @@
         <v>11.9627</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.643</v>
+        <v>0.3845</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.4815</v>
+        <v>-1.4538</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8384</v>
+        <v>1.8383</v>
       </c>
       <c r="V12" t="n">
         <v>2.825</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.0803</v>
+        <v>2.5665</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2246</v>
+        <v>0.7775</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8557</v>
+        <v>1.789</v>
       </c>
       <c r="G13" t="n">
         <v>-0.9878</v>
@@ -1468,13 +1468,13 @@
         <v>0.2175</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8512</v>
+        <v>0.3374</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2656</v>
+        <v>-0.1815</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5856</v>
+        <v>0.5188</v>
       </c>
       <c r="V13" t="n">
         <v>2.9995</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5798</v>
+        <v>1.348</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.0268</v>
+        <v>-0.8033</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6067</v>
+        <v>2.1513</v>
       </c>
       <c r="G14" t="n">
         <v>0.8525</v>
@@ -1546,13 +1546,13 @@
         <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9676</v>
+        <v>-0.1995</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7619</v>
+        <v>-0.5383</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2057</v>
+        <v>0.3389</v>
       </c>
       <c r="V14" t="n">
         <v>1.13</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>D. SARAIVA SEIXAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0447</v>
+        <v>0.4426</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.4654</v>
+        <v>-1.0651</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5101</v>
+        <v>1.5077</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1677</v>
+        <v>-0.5629</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2068</v>
+        <v>-1.6363</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3745</v>
+        <v>1.0734</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.1731</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-1.4354</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2661</v>
+        <v>1.2622</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1178</v>
+        <v>-0.3898</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4772</v>
+        <v>-0.2009</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6407</v>
+        <v>-0.1889</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1751</v>
+        <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2551</v>
+        <v>0.7451</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4278</v>
+        <v>0.3701</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1727</v>
+        <v>0.3749</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9554</v>
+        <v>-0.1745</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.1745</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. HUGUET CARRASCO</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2026</v>
+        <v>0.213</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1211</v>
+        <v>-2.3537</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.08160000000000001</v>
+        <v>2.5667</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7766</v>
+        <v>0.1677</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0881</v>
+        <v>-0.2068</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6885</v>
+        <v>0.3745</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5639</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6205000000000001</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0566</v>
+        <v>-0.2661</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2127</v>
+        <v>1.1178</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5324</v>
+        <v>0.4772</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7451</v>
+        <v>0.6407</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6525</v>
+        <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3887</v>
+        <v>-0.0868</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.316</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2962</v>
+        <v>0.2292</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.243</v>
+        <v>-0.9554</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.243</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. SARAIVA SEIXAS</t>
+          <t>S. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3024</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.5121</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2097</v>
+        <v>0.0725</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5629</v>
+        <v>0.7766</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6363</v>
+        <v>0.0881</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0734</v>
+        <v>0.6885</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1731</v>
+        <v>0.5639</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.4354</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2622</v>
+        <v>-0.0566</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3898</v>
+        <v>0.2127</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2009</v>
+        <v>-0.5324</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1889</v>
+        <v>0.7451</v>
       </c>
       <c r="P17" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>-0</v>
+        <v>-0.1229</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0769</v>
+        <v>-0.5732</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0769</v>
+        <v>0.4503</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1745</v>
+        <v>-1.243</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.1745</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. KALSCHEUR</t>
+          <t>A. VRABAC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9063</v>
+        <v>-0.5681</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3686</v>
+        <v>-1.6812</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4623</v>
+        <v>1.1131</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.3661</v>
+        <v>-2.1951</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.401</v>
+        <v>-2.427</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.965</v>
+        <v>0.2319</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.5078</v>
+        <v>-1.3424</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3491</v>
+        <v>-1.3806</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.1587</v>
+        <v>0.0382</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1417</v>
+        <v>-0.8528</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0519</v>
+        <v>-1.0464</v>
       </c>
       <c r="O18" t="n">
         <v>0.1936</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8274</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1392</v>
+        <v>-0.3389</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3118</v>
+        <v>0.4041</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.3252</v>
+        <v>0.2568</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3252</v>
+        <v>0.2568</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0047</v>
+        <v>-1.6948</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6618</v>
+        <v>-0.841</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6571</v>
+        <v>-0.8538</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.6908</v>
+        <v>-0.3792</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.5402</v>
+        <v>-1.2167</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1506</v>
+        <v>0.8375</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.6045</v>
+        <v>-0.2714</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.6428</v>
+        <v>-0.6173</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0382</v>
+        <v>0.3459</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0863</v>
+        <v>-0.1077</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8974</v>
+        <v>-0.5994</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1889</v>
+        <v>0.4916</v>
       </c>
       <c r="P19" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>2.7577</v>
+        <v>0.1427</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4238</v>
+        <v>-0.5696</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3338</v>
+        <v>0.7123</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4934</v>
+        <v>-2.7634</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6064000000000001</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.113</v>
+        <v>-2.7634</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. VRABAC</t>
+          <t>G. KALSCHEUR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5804</v>
+        <v>-1.7208</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5753</v>
+        <v>-2.4862</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9949</v>
+        <v>0.7654</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1951</v>
+        <v>-2.3661</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.427</v>
+        <v>-0.401</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2319</v>
+        <v>-1.965</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3424</v>
+        <v>-2.5078</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3806</v>
+        <v>-0.3491</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0382</v>
+        <v>-2.1587</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8528</v>
+        <v>0.1417</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0464</v>
+        <v>-0.0519</v>
       </c>
       <c r="O20" t="n">
         <v>0.1936</v>
       </c>
       <c r="P20" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9471000000000001</v>
+        <v>0.0129</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2329</v>
+        <v>0.0216</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2859</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2568</v>
+        <v>-1.3252</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.2568</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0994</v>
+        <v>-2.4127</v>
       </c>
       <c r="E21" t="n">
         <v>-4.9057</v>
       </c>
       <c r="F21" t="n">
-        <v>2.8063</v>
+        <v>2.493</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0753</v>
@@ -2092,13 +2092,13 @@
         <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.3374</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0769</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7276</v>
+        <v>0.4143</v>
       </c>
       <c r="V21" t="n">
         <v>0.1952</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0038</v>
+        <v>-2.8545</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8469</v>
+        <v>-3.45</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1569</v>
+        <v>0.5955</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3792</v>
+        <v>-4.6908</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2167</v>
+        <v>-4.5402</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8375</v>
+        <v>-0.1506</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2714</v>
+        <v>-3.6045</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6173</v>
+        <v>-3.6428</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3459</v>
+        <v>0.0382</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1077</v>
+        <v>-1.0863</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5994</v>
+        <v>-0.8974</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4916</v>
+        <v>-0.1889</v>
       </c>
       <c r="P22" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1662</v>
+        <v>0.9079</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.5754</v>
+        <v>0.6357</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4092</v>
+        <v>0.2722</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.7634</v>
+        <v>0.4934</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.7634</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8607</v>
+        <v>-3.0977</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6686</v>
+        <v>-1.998</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1921</v>
+        <v>-1.0996</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2558</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7964</v>
+        <v>-0.0333</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.0829</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0429</v>
+        <v>0.0496</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5034</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1669</v>
+        <v>-4.217</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4721</v>
+        <v>-3.5839</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6948</v>
+        <v>-0.6331</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7867</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0772</v>
+        <v>0.027</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0769</v>
+        <v>-0.1887</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1541</v>
+        <v>0.2157</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9347</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-13.4224</v>
+        <v>-11.9323</v>
       </c>
       <c r="E25" t="n">
-        <v>-22.3998</v>
+        <v>-22.3999</v>
       </c>
       <c r="F25" t="n">
-        <v>8.977399999999999</v>
+        <v>10.4677</v>
       </c>
       <c r="G25" t="n">
         <v>-14.5029</v>
@@ -2383,10 +2383,10 @@
         <v>-15.1273</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.6214999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>0.002500000000000169</v>
+        <v>0.002499999999999836</v>
       </c>
       <c r="N25" t="n">
         <v>-1.9336</v>
@@ -2404,13 +2404,13 @@
         <v>15.2253</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6430999999999999</v>
+        <v>2.1331</v>
       </c>
       <c r="T25" t="n">
         <v>-1.8386</v>
       </c>
       <c r="U25" t="n">
-        <v>2.4816</v>
+        <v>3.9716</v>
       </c>
       <c r="V25" t="n">
         <v>-2.8247</v>
